--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.657830235493575</v>
+        <v>3.134495051956541</v>
       </c>
       <c r="C2">
-        <v>2.002151662949332</v>
+        <v>1.89978048597444</v>
       </c>
       <c r="D2">
-        <v>1.570172298926857</v>
+        <v>1.525480897030672</v>
       </c>
       <c r="E2">
-        <v>1.378958854892205</v>
+        <v>1.376764628851521</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.555220259392244</v>
+        <v>3.015854961770917</v>
       </c>
       <c r="C3">
-        <v>1.971045113597998</v>
+        <v>1.849965429311619</v>
       </c>
       <c r="D3">
-        <v>1.558931202156377</v>
+        <v>1.509979415128001</v>
       </c>
       <c r="E3">
-        <v>1.372112685789045</v>
+        <v>1.368056543576119</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.607583539008171</v>
+        <v>3.032258512684339</v>
       </c>
       <c r="C4">
-        <v>1.993043150492128</v>
+        <v>1.854084167162709</v>
       </c>
       <c r="D4">
-        <v>1.572365048458049</v>
+        <v>1.507478430886973</v>
       </c>
       <c r="E4">
-        <v>1.383240013895821</v>
+        <v>1.365558243147134</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.534977467695962</v>
+        <v>3.020198916730894</v>
       </c>
       <c r="C5">
-        <v>2.020387323550141</v>
+        <v>1.876641087897798</v>
       </c>
       <c r="D5">
-        <v>1.57880164550358</v>
+        <v>1.511869181539962</v>
       </c>
       <c r="E5">
-        <v>1.399850874782828</v>
+        <v>1.379657500535665</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.968124494335747</v>
+        <v>2.957570778913098</v>
       </c>
       <c r="C6">
-        <v>1.875463510908506</v>
+        <v>1.857956759342698</v>
       </c>
       <c r="D6">
-        <v>1.548287313870725</v>
+        <v>1.506851313985656</v>
       </c>
       <c r="E6">
-        <v>1.384591965316204</v>
+        <v>1.376020463996002</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.230341905891172</v>
+        <v>2.822587674333881</v>
       </c>
       <c r="C7">
-        <v>1.961212458634178</v>
+        <v>1.834978711092352</v>
       </c>
       <c r="D7">
-        <v>1.587202116579776</v>
+        <v>1.531291161080332</v>
       </c>
       <c r="E7">
-        <v>1.390972419996553</v>
+        <v>1.383621814052024</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.048578856136536</v>
+        <v>2.916054834127292</v>
       </c>
       <c r="C8">
-        <v>1.497617726625957</v>
+        <v>1.767272091689032</v>
       </c>
       <c r="D8">
-        <v>1.347264377506428</v>
+        <v>1.45737305922209</v>
       </c>
       <c r="E8">
-        <v>1.307684694103237</v>
+        <v>1.325207859392255</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.836812886854931</v>
+        <v>2.709360718102916</v>
       </c>
       <c r="C9">
-        <v>1.812437534362182</v>
+        <v>1.766819276858553</v>
       </c>
       <c r="D9">
-        <v>1.524252566768622</v>
+        <v>1.489181574708383</v>
       </c>
       <c r="E9">
-        <v>1.359680543457173</v>
+        <v>1.35583694564875</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3.499139607109543</v>
+        <v>2.88553404380982</v>
       </c>
       <c r="C10">
-        <v>2.033644326230509</v>
+        <v>1.854518068625072</v>
       </c>
       <c r="D10">
-        <v>1.602662455506086</v>
+        <v>1.526806511154333</v>
       </c>
       <c r="E10">
-        <v>1.403891052508207</v>
+        <v>1.381485396026643</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.480833426149434</v>
+        <v>2.859617916280834</v>
       </c>
       <c r="C11">
-        <v>2.025370691254477</v>
+        <v>1.845563763123255</v>
       </c>
       <c r="D11">
-        <v>1.599602480699534</v>
+        <v>1.523495796495839</v>
       </c>
       <c r="E11">
-        <v>1.400737064552015</v>
+        <v>1.37830874562257</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>3.018377456737966</v>
+        <v>2.463130732023072</v>
       </c>
       <c r="C12">
-        <v>1.892787997103477</v>
+        <v>1.720672658826846</v>
       </c>
       <c r="D12">
-        <v>1.56334331424269</v>
+        <v>1.488518234650031</v>
       </c>
       <c r="E12">
-        <v>1.373175483619288</v>
+        <v>1.351087570385829</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3.337211194759396</v>
+        <v>2.752945576217339</v>
       </c>
       <c r="C13">
-        <v>1.989697056952975</v>
+        <v>1.814690078601969</v>
       </c>
       <c r="D13">
-        <v>1.587080947628143</v>
+        <v>1.511740355344143</v>
       </c>
       <c r="E13">
-        <v>1.392783088423188</v>
+        <v>1.370516843988449</v>
       </c>
     </row>
   </sheetData>
